--- a/Lenguaje/BasicVerb.xlsx
+++ b/Lenguaje/BasicVerb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upvedues-my.sharepoint.com/personal/zyyeche_upv_edu_es/Documents/Thalassar/Colangs/Lenguaje/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="11_AD4D2F04E46CFB4ACB3E20196D56F008693EDF13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CB0DD65-2CA8-4F8A-A778-76B074166108}"/>
+  <xr:revisionPtr revIDLastSave="229" documentId="11_AD4D2F04E46CFB4ACB3E20196D56F008693EDF13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98C42C61-4A8E-47EB-9083-89875F8A005B}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="100">
   <si>
     <t>Columna1</t>
   </si>
@@ -325,6 +325,110 @@
   </si>
   <si>
     <t>感官系动词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Volar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lisser</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Florar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必须</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打破、破坏、损坏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Luminar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vidar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zephir</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kombatar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skolir</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kriar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sensar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thermar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开花、绽放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发光、照亮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预见、预知</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>疾行、竞走</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗、斗争</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学习</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创造、构建</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感知、感觉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>温暖、保暖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bregar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Moker</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -332,7 +436,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -362,6 +466,21 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -383,71 +502,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <font>
         <strike val="0"/>
@@ -699,58 +764,58 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7F9F94AD-7A50-4535-8AA6-08A165ADE883}" name="Tabla2" displayName="Tabla2" ref="G5:I22" headerRowDxfId="17" dataDxfId="15" totalsRowDxfId="16">
-  <autoFilter ref="G5:I22" xr:uid="{7F9F94AD-7A50-4535-8AA6-08A165ADE883}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G6:I26">
-    <sortCondition ref="G22:G26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7F9F94AD-7A50-4535-8AA6-08A165ADE883}" name="Tabla2" displayName="Tabla2" ref="G5:I31" headerRowDxfId="16" dataDxfId="15" totalsRowDxfId="14">
+  <autoFilter ref="G5:I31" xr:uid="{7F9F94AD-7A50-4535-8AA6-08A165ADE883}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G6:I31">
+    <sortCondition ref="G5:G31"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="6" xr3:uid="{6316E6A9-226C-4042-8610-D066846E48BD}" name="Columna6" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{24CB9A25-AC85-4D9E-8E02-909F22E13DC3}" name="Columna7" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{B0ECFE13-5212-48BA-A715-7B30FA5A2A75}" name="Columna8" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{6316E6A9-226C-4042-8610-D066846E48BD}" name="Columna6" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{24CB9A25-AC85-4D9E-8E02-909F22E13DC3}" name="Columna7" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{B0ECFE13-5212-48BA-A715-7B30FA5A2A75}" name="Columna8" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6C979631-5102-490E-890E-7B038FB9D301}" name="Tabla3" displayName="Tabla3" ref="C34:E41" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="C34:E41" xr:uid="{6C979631-5102-490E-890E-7B038FB9D301}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C35:E46">
-    <sortCondition ref="C35:C46"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6C979631-5102-490E-890E-7B038FB9D301}" name="Tabla3" displayName="Tabla3" ref="K5:K14" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="K5:K14" xr:uid="{6C979631-5102-490E-890E-7B038FB9D301}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K6:K14">
+    <sortCondition ref="K5:K14"/>
   </sortState>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{7B8561BE-C7CF-453A-8374-94C20FF18861}" name="Columna1" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{215BB886-67FC-4359-BEC9-EFE2DDB6BA96}" name="Columna2" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{F36522E4-FA35-4784-BB4C-14E3AD4E32C0}" name="Columna3" dataDxfId="12"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{7B8561BE-C7CF-453A-8374-94C20FF18861}" name="Columna1" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E554A806-B109-41DC-AB8B-DE5AA3F629BB}" name="Tabla4" displayName="Tabla4" ref="G34:I47" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="G34:I47" xr:uid="{E554A806-B109-41DC-AB8B-DE5AA3F629BB}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G35:I47">
-    <sortCondition ref="G35:G47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E554A806-B109-41DC-AB8B-DE5AA3F629BB}" name="Tabla4" displayName="Tabla4" ref="M5:M28" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="M5:M28" xr:uid="{E554A806-B109-41DC-AB8B-DE5AA3F629BB}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M6:M28">
+    <sortCondition ref="M5:M28"/>
   </sortState>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8F6C8787-B41D-4CFF-85CD-C28C1A6CC2F8}" name="Columna1" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{41359468-082D-4C4F-960F-D445CFFABC61}" name="Columna2" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{ABFA4DA6-4845-4267-9D50-E63141DC7500}" name="Columna3" dataDxfId="7"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{8F6C8787-B41D-4CFF-85CD-C28C1A6CC2F8}" name="Columna1" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{83D94E6C-11D8-4CC5-9537-9148E71539B9}" name="Tabla5" displayName="Tabla5" ref="C5:E10" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
-  <autoFilter ref="C5:E10" xr:uid="{83D94E6C-11D8-4CC5-9537-9148E71539B9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{83D94E6C-11D8-4CC5-9537-9148E71539B9}" name="Tabla5" displayName="Tabla5" ref="C5:E13" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="C5:E13" xr:uid="{83D94E6C-11D8-4CC5-9537-9148E71539B9}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{F7002419-1A5A-4A08-977F-78820592207A}" name="Columna1" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{0E6C38E7-EBC8-45FA-87B5-8071D7FC6457}" name="Columna2" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{7722EE7A-4A8A-4048-B9C0-590DC50D2638}" name="Columna3" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{F7002419-1A5A-4A08-977F-78820592207A}" name="Columna1" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{0E6C38E7-EBC8-45FA-87B5-8071D7FC6457}" name="Columna2" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{7722EE7A-4A8A-4048-B9C0-590DC50D2638}" name="Columna3" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1019,20 +1084,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C4:I47"/>
+  <dimension ref="C4:M53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="14.5" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="4" max="4" width="22.25" customWidth="1"/>
     <col min="5" max="5" width="13.875" customWidth="1"/>
     <col min="6" max="6" width="5.125" customWidth="1"/>
     <col min="7" max="7" width="13.75" customWidth="1"/>
     <col min="8" max="8" width="16.125" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="11.375" customWidth="1"/>
+    <col min="10" max="10" width="24.75" customWidth="1"/>
+    <col min="11" max="11" width="14.25" customWidth="1"/>
+    <col min="12" max="12" width="3.375" customWidth="1"/>
+    <col min="13" max="13" width="22.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C4" s="1" t="s">
         <v>71</v>
       </c>
@@ -1044,8 +1112,14 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="K4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
         <v>0</v>
       </c>
@@ -1065,8 +1139,14 @@
       <c r="I5" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="K5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
@@ -1086,8 +1166,14 @@
       <c r="I6" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="K6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1107,8 +1193,14 @@
       <c r="I7" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="8" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="K7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1128,8 +1220,14 @@
       <c r="I8" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="9" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="K8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
@@ -1149,10 +1247,20 @@
       <c r="I9" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="10" spans="3:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="K9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="3:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="C10" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="E10" s="2"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
@@ -1164,11 +1272,21 @@
       <c r="I10" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="11" spans="3:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="K10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="3:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="C11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="2"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
         <v>48</v>
@@ -1179,402 +1297,444 @@
       <c r="I11" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" spans="3:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="K11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="3:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="C12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="2"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="3:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
+      <c r="G12" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="K12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="3:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="C13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="2"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="3:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="3:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="G14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="M14" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="G15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="M15" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="M16" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="G18" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="M18" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
-      <c r="G22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="G22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="M22" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="24" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="G23" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="M23" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-    </row>
-    <row r="25" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="G24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="G25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I25" s="2"/>
+      <c r="M25" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="G26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-    </row>
-    <row r="28" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="G27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="G28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M28" s="2"/>
+    </row>
+    <row r="29" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="G29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="G30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="G31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I31" s="2"/>
+    </row>
+    <row r="32" spans="3:13" ht="18" x14ac:dyDescent="0.25">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
     </row>
     <row r="33" spans="3:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="C33" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
-      <c r="G33" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
     </row>
     <row r="34" spans="3:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="C34" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
       <c r="F34" s="1"/>
-      <c r="G34" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
     </row>
     <row r="35" spans="3:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="C35" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
-      <c r="G35" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" spans="3:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="C36" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
-      <c r="G36" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
     </row>
     <row r="37" spans="3:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="C37" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
-      <c r="G37" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
     </row>
     <row r="38" spans="3:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="C38" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
-      <c r="G38" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
     <row r="39" spans="3:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="C39" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
-      <c r="G39" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
     <row r="40" spans="3:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
     <row r="41" spans="3:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
     </row>
     <row r="42" spans="3:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
     <row r="43" spans="3:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
       <c r="F43" s="1"/>
-      <c r="G43" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
@@ -1583,9 +1743,6 @@
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-      <c r="G44" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
@@ -1594,9 +1751,6 @@
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
@@ -1605,9 +1759,6 @@
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
@@ -1616,9 +1767,32 @@
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
+    </row>
+    <row r="48" spans="3:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+    </row>
+    <row r="49" spans="8:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+    </row>
+    <row r="50" spans="8:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+    </row>
+    <row r="51" spans="8:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+    </row>
+    <row r="52" spans="8:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+    </row>
+    <row r="53" spans="8:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
